--- a/data/miteinanderProject/04_Gemeinsame_Stadtteilaktivitaeten_Mockdaten.xlsx
+++ b/data/miteinanderProject/04_Gemeinsame_Stadtteilaktivitaeten_Mockdaten.xlsx
@@ -114,17 +114,17 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DistrictFeedback" displayName="DistrictFeedback" ref="A1:F39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="6">
-    <x:tableColumn id="1" name="Feedback-ID"/>
-    <x:tableColumn id="2" name="Teilnehmenden-ID"/>
-    <x:tableColumn id="3" name="Aktivitäts-ID"/>
-    <x:tableColumn id="4" name="Befragungsdatum"/>
-    <x:tableColumn id="5" name="Zufriedenheit (1-5)"/>
-    <x:tableColumn id="6" name="Kommentar"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DistrictFeedback" displayName="DistrictFeedback" ref="A1:F42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <tableColumns count="6">
+    <tableColumn id="1" name="Feedback-ID"/>
+    <tableColumn id="2" name="Teilnehmenden-ID"/>
+    <tableColumn id="3" name="Aktivitäts-ID"/>
+    <tableColumn id="4" name="Befragungsdatum"/>
+    <tableColumn id="5" name="Zufriedenheit (1-5)"/>
+    <tableColumn id="6" name="Kommentar"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1587,801 +1587,885 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="9.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.5" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="8" t="str">
-        <x:v>Feedback-ID</x:v>
-      </x:c>
-      <x:c r="B1" s="8" t="str">
-        <x:v>Teilnehmenden-ID</x:v>
-      </x:c>
-      <x:c r="C1" s="8" t="str">
-        <x:v>Aktivitäts-ID</x:v>
-      </x:c>
-      <x:c r="D1" s="12" t="str">
-        <x:v>Befragungsdatum</x:v>
-      </x:c>
-      <x:c r="E1" s="8" t="str">
-        <x:v>Zufriedenheit (1-5)</x:v>
-      </x:c>
-      <x:c r="F1" s="8" t="str">
-        <x:v>Kommentar</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="9" t="str">
-        <x:v>FB-001</x:v>
-      </x:c>
-      <x:c r="B2" s="9" t="str">
-        <x:v>ST-030</x:v>
-      </x:c>
-      <x:c r="C2" s="9" t="str">
-        <x:v>STA-07</x:v>
-      </x:c>
-      <x:c r="D2" s="9" t="n">
-        <x:v>46040</x:v>
-      </x:c>
-      <x:c r="E2" s="9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F2" s="9" t="str">
-        <x:v>Schöne gemeinsame Aktivität.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="9" t="str">
-        <x:v>FB-002</x:v>
-      </x:c>
-      <x:c r="B3" s="9" t="str">
-        <x:v>ST-026</x:v>
-      </x:c>
-      <x:c r="C3" s="9" t="str">
-        <x:v>STA-06</x:v>
-      </x:c>
-      <x:c r="D3" s="9" t="n">
-        <x:v>45970</x:v>
-      </x:c>
-      <x:c r="E3" s="9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F3" s="9" t="str">
-        <x:v>Schöne gemeinsame Aktivität.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="9" t="str">
-        <x:v>FB-003</x:v>
-      </x:c>
-      <x:c r="B4" s="9" t="str">
-        <x:v>ST-033</x:v>
-      </x:c>
-      <x:c r="C4" s="9" t="str">
-        <x:v>STA-01</x:v>
-      </x:c>
-      <x:c r="D4" s="9" t="n">
-        <x:v>45823</x:v>
-      </x:c>
-      <x:c r="E4" s="9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F4" s="9" t="str">
-        <x:v>Gute Gelegenheit, andere kennenzulernen.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="9" t="str">
-        <x:v>FB-004</x:v>
-      </x:c>
-      <x:c r="B5" s="9" t="str">
-        <x:v>ST-022</x:v>
-      </x:c>
-      <x:c r="C5" s="9" t="str">
-        <x:v>STA-03</x:v>
-      </x:c>
-      <x:c r="D5" s="9" t="n">
-        <x:v>45886</x:v>
-      </x:c>
-      <x:c r="E5" s="9" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F5" s="9" t="str">
-        <x:v>Für mich nicht ganz passend.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="9" t="str">
-        <x:v>FB-005</x:v>
-      </x:c>
-      <x:c r="B6" s="9" t="str">
-        <x:v>ST-031</x:v>
-      </x:c>
-      <x:c r="C6" s="9" t="str">
-        <x:v>STA-05</x:v>
-      </x:c>
-      <x:c r="D6" s="9" t="n">
-        <x:v>45942</x:v>
-      </x:c>
-      <x:c r="E6" s="9" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F6" s="9" t="str">
-        <x:v>Für mich nicht ganz passend.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="9" t="str">
-        <x:v>FB-006</x:v>
-      </x:c>
-      <x:c r="B7" s="9" t="str">
-        <x:v>ST-021</x:v>
-      </x:c>
-      <x:c r="C7" s="9" t="str">
-        <x:v>STA-07</x:v>
-      </x:c>
-      <x:c r="D7" s="9" t="n">
-        <x:v>46040</x:v>
-      </x:c>
-      <x:c r="E7" s="9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F7" s="9" t="str">
-        <x:v>Gerne wieder.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="9" t="str">
-        <x:v>FB-007</x:v>
-      </x:c>
-      <x:c r="B8" s="9" t="str">
-        <x:v>ST-034</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="str">
-        <x:v>STA-06</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="n">
-        <x:v>45970</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="str">
-        <x:v>Gerne wieder.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="9" t="str">
-        <x:v>FB-008</x:v>
-      </x:c>
-      <x:c r="B9" s="9" t="str">
-        <x:v>ST-002</x:v>
-      </x:c>
-      <x:c r="C9" s="9" t="str">
-        <x:v>STA-06</x:v>
-      </x:c>
-      <x:c r="D9" s="9" t="n">
-        <x:v>45970</x:v>
-      </x:c>
-      <x:c r="E9" s="9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F9" s="9" t="str">
-        <x:v>Schöne gemeinsame Aktivität.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="9" t="str">
-        <x:v>FB-009</x:v>
-      </x:c>
-      <x:c r="B10" s="9" t="str">
-        <x:v>ST-017</x:v>
-      </x:c>
-      <x:c r="C10" s="9" t="str">
-        <x:v>STA-06</x:v>
-      </x:c>
-      <x:c r="D10" s="9" t="n">
-        <x:v>45970</x:v>
-      </x:c>
-      <x:c r="E10" s="9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F10" s="9" t="str">
-        <x:v>Ich habe mich wohlgefühlt.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="9" t="str">
-        <x:v>FB-010</x:v>
-      </x:c>
-      <x:c r="B11" s="9" t="str">
-        <x:v>ST-014</x:v>
-      </x:c>
-      <x:c r="C11" s="9" t="str">
-        <x:v>STA-05</x:v>
-      </x:c>
-      <x:c r="D11" s="9" t="n">
-        <x:v>45942</x:v>
-      </x:c>
-      <x:c r="E11" s="9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F11" s="9" t="str">
-        <x:v>Gerne wieder.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="9" t="str">
-        <x:v>FB-011</x:v>
-      </x:c>
-      <x:c r="B12" s="9" t="str">
-        <x:v>ST-030</x:v>
-      </x:c>
-      <x:c r="C12" s="9" t="str">
-        <x:v>STA-06</x:v>
-      </x:c>
-      <x:c r="D12" s="9" t="n">
-        <x:v>45970</x:v>
-      </x:c>
-      <x:c r="E12" s="9" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F12" s="9" t="str">
-        <x:v>Organisation könnte klarer sein.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="9" t="str">
-        <x:v>FB-012</x:v>
-      </x:c>
-      <x:c r="B13" s="9" t="str">
-        <x:v>ST-008</x:v>
-      </x:c>
-      <x:c r="C13" s="9" t="str">
-        <x:v>STA-06</x:v>
-      </x:c>
-      <x:c r="D13" s="9" t="n">
-        <x:v>45970</x:v>
-      </x:c>
-      <x:c r="E13" s="9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F13" s="9" t="str">
-        <x:v>Gerne wieder.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="9" t="str">
-        <x:v>FB-013</x:v>
-      </x:c>
-      <x:c r="B14" s="9" t="str">
-        <x:v>ST-009</x:v>
-      </x:c>
-      <x:c r="C14" s="9" t="str">
-        <x:v>STA-02</x:v>
-      </x:c>
-      <x:c r="D14" s="9" t="n">
-        <x:v>45844</x:v>
-      </x:c>
-      <x:c r="E14" s="9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F14" s="9" t="str">
-        <x:v>Ich habe mich wohlgefühlt.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="9" t="str">
-        <x:v>FB-014</x:v>
-      </x:c>
-      <x:c r="B15" s="9" t="str">
-        <x:v>ST-008</x:v>
-      </x:c>
-      <x:c r="C15" s="9" t="str">
-        <x:v>STA-01</x:v>
-      </x:c>
-      <x:c r="D15" s="9" t="n">
-        <x:v>45823</x:v>
-      </x:c>
-      <x:c r="E15" s="9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F15" s="9" t="str">
-        <x:v>Gute Gelegenheit, andere kennenzulernen.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="9" t="str">
-        <x:v>FB-015</x:v>
-      </x:c>
-      <x:c r="B16" s="9" t="str">
-        <x:v>ST-027</x:v>
-      </x:c>
-      <x:c r="C16" s="9" t="str">
-        <x:v>STA-06</x:v>
-      </x:c>
-      <x:c r="D16" s="9" t="n">
-        <x:v>45970</x:v>
-      </x:c>
-      <x:c r="E16" s="9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F16" s="9" t="str">
-        <x:v>Gute Gelegenheit, andere kennenzulernen.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="9" t="str">
-        <x:v>FB-016</x:v>
-      </x:c>
-      <x:c r="B17" s="9" t="str">
-        <x:v>ST-029</x:v>
-      </x:c>
-      <x:c r="C17" s="9" t="str">
-        <x:v>STA-05</x:v>
-      </x:c>
-      <x:c r="D17" s="9" t="n">
-        <x:v>45942</x:v>
-      </x:c>
-      <x:c r="E17" s="9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F17" s="9" t="str">
-        <x:v>Gerne wieder.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="9" t="str">
-        <x:v>FB-017</x:v>
-      </x:c>
-      <x:c r="B18" s="9" t="str">
-        <x:v>ST-030</x:v>
-      </x:c>
-      <x:c r="C18" s="9" t="str">
-        <x:v>STA-05</x:v>
-      </x:c>
-      <x:c r="D18" s="9" t="n">
-        <x:v>45942</x:v>
-      </x:c>
-      <x:c r="E18" s="9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F18" s="9" t="str">
-        <x:v>Gerne wieder.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="9" t="str">
-        <x:v>FB-018</x:v>
-      </x:c>
-      <x:c r="B19" s="9" t="str">
-        <x:v>ST-026</x:v>
-      </x:c>
-      <x:c r="C19" s="9" t="str">
-        <x:v>STA-03</x:v>
-      </x:c>
-      <x:c r="D19" s="9" t="n">
-        <x:v>45886</x:v>
-      </x:c>
-      <x:c r="E19" s="9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F19" s="9" t="str">
-        <x:v>Ich habe mich wohlgefühlt.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="9" t="str">
-        <x:v>FB-019</x:v>
-      </x:c>
-      <x:c r="B20" s="9" t="str">
-        <x:v>ST-029</x:v>
-      </x:c>
-      <x:c r="C20" s="9" t="str">
-        <x:v>STA-03</x:v>
-      </x:c>
-      <x:c r="D20" s="9" t="n">
-        <x:v>45886</x:v>
-      </x:c>
-      <x:c r="E20" s="9" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F20" s="9" t="str">
-        <x:v>Organisation könnte klarer sein.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="9" t="str">
-        <x:v>FB-020</x:v>
-      </x:c>
-      <x:c r="B21" s="9" t="str">
-        <x:v>ST-028</x:v>
-      </x:c>
-      <x:c r="C21" s="9" t="str">
-        <x:v>STA-08</x:v>
-      </x:c>
-      <x:c r="D21" s="9" t="n">
-        <x:v>46068</x:v>
-      </x:c>
-      <x:c r="E21" s="9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F21" s="9" t="str">
-        <x:v>Schöne gemeinsame Aktivität.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="9" t="str">
-        <x:v>FB-021</x:v>
-      </x:c>
-      <x:c r="B22" s="9" t="str">
-        <x:v>ST-018</x:v>
-      </x:c>
-      <x:c r="C22" s="9" t="str">
-        <x:v>STA-03</x:v>
-      </x:c>
-      <x:c r="D22" s="9" t="n">
-        <x:v>45886</x:v>
-      </x:c>
-      <x:c r="E22" s="9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F22" s="9" t="str">
-        <x:v>Ich habe mich wohlgefühlt.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="9" t="str">
-        <x:v>FB-022</x:v>
-      </x:c>
-      <x:c r="B23" s="9" t="str">
-        <x:v>ST-021</x:v>
-      </x:c>
-      <x:c r="C23" s="9" t="str">
-        <x:v>STA-02</x:v>
-      </x:c>
-      <x:c r="D23" s="9" t="n">
-        <x:v>45844</x:v>
-      </x:c>
-      <x:c r="E23" s="9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F23" s="9" t="str">
-        <x:v>Schöne gemeinsame Aktivität.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="9" t="str">
-        <x:v>FB-023</x:v>
-      </x:c>
-      <x:c r="B24" s="9" t="str">
-        <x:v>ST-013</x:v>
-      </x:c>
-      <x:c r="C24" s="9" t="str">
-        <x:v>STA-02</x:v>
-      </x:c>
-      <x:c r="D24" s="9" t="n">
-        <x:v>45844</x:v>
-      </x:c>
-      <x:c r="E24" s="9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F24" s="9" t="str">
-        <x:v>Gute Gelegenheit, andere kennenzulernen.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="9" t="str">
-        <x:v>FB-024</x:v>
-      </x:c>
-      <x:c r="B25" s="9" t="str">
-        <x:v>ST-031</x:v>
-      </x:c>
-      <x:c r="C25" s="9" t="str">
-        <x:v>STA-03</x:v>
-      </x:c>
-      <x:c r="D25" s="9" t="n">
-        <x:v>45886</x:v>
-      </x:c>
-      <x:c r="E25" s="9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F25" s="9" t="str">
-        <x:v>Schöne gemeinsame Aktivität.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="9" t="str">
-        <x:v>FB-025</x:v>
-      </x:c>
-      <x:c r="B26" s="9" t="str">
-        <x:v>ST-031</x:v>
-      </x:c>
-      <x:c r="C26" s="9" t="str">
-        <x:v>STA-07</x:v>
-      </x:c>
-      <x:c r="D26" s="9" t="n">
-        <x:v>46040</x:v>
-      </x:c>
-      <x:c r="E26" s="9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F26" s="9" t="str">
-        <x:v>Gute Gelegenheit, andere kennenzulernen.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="9" t="str">
-        <x:v>FB-026</x:v>
-      </x:c>
-      <x:c r="B27" s="9" t="str">
-        <x:v>ST-023</x:v>
-      </x:c>
-      <x:c r="C27" s="9" t="str">
-        <x:v>STA-02</x:v>
-      </x:c>
-      <x:c r="D27" s="9" t="n">
-        <x:v>45844</x:v>
-      </x:c>
-      <x:c r="E27" s="9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F27" s="9" t="str">
-        <x:v>Ich habe mich wohlgefühlt.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="9" t="str">
-        <x:v>FB-027</x:v>
-      </x:c>
-      <x:c r="B28" s="9" t="str">
-        <x:v>ST-015</x:v>
-      </x:c>
-      <x:c r="C28" s="9" t="str">
-        <x:v>STA-06</x:v>
-      </x:c>
-      <x:c r="D28" s="9" t="n">
-        <x:v>45970</x:v>
-      </x:c>
-      <x:c r="E28" s="9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F28" s="9" t="str">
-        <x:v>Gute Gelegenheit, andere kennenzulernen.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="9" t="str">
-        <x:v>FB-028</x:v>
-      </x:c>
-      <x:c r="B29" s="9" t="str">
-        <x:v>ST-033</x:v>
-      </x:c>
-      <x:c r="C29" s="9" t="str">
-        <x:v>STA-07</x:v>
-      </x:c>
-      <x:c r="D29" s="9" t="n">
-        <x:v>46040</x:v>
-      </x:c>
-      <x:c r="E29" s="9" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F29" s="9" t="str">
-        <x:v>Für mich nicht ganz passend.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="9" t="str">
-        <x:v>FB-029</x:v>
-      </x:c>
-      <x:c r="B30" s="9" t="str">
-        <x:v>ST-005</x:v>
-      </x:c>
-      <x:c r="C30" s="9" t="str">
-        <x:v>STA-03</x:v>
-      </x:c>
-      <x:c r="D30" s="9" t="n">
-        <x:v>45886</x:v>
-      </x:c>
-      <x:c r="E30" s="9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F30" s="9" t="str">
-        <x:v>Schöne gemeinsame Aktivität.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="9" t="str">
-        <x:v>FB-030</x:v>
-      </x:c>
-      <x:c r="B31" s="9" t="str">
-        <x:v>ST-001</x:v>
-      </x:c>
-      <x:c r="C31" s="9" t="str">
-        <x:v>STA-06</x:v>
-      </x:c>
-      <x:c r="D31" s="9" t="n">
-        <x:v>45970</x:v>
-      </x:c>
-      <x:c r="E31" s="9" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F31" s="9" t="str">
-        <x:v>War in Ordnung, aber etwas lang.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="9" t="str">
-        <x:v>FB-031</x:v>
-      </x:c>
-      <x:c r="B32" s="9" t="str">
-        <x:v>ST-005</x:v>
-      </x:c>
-      <x:c r="C32" s="9" t="str">
-        <x:v>STA-05</x:v>
-      </x:c>
-      <x:c r="D32" s="9" t="n">
-        <x:v>45942</x:v>
-      </x:c>
-      <x:c r="E32" s="9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F32" s="9" t="str">
-        <x:v>Schöne gemeinsame Aktivität.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="9" t="str">
-        <x:v>FB-032</x:v>
-      </x:c>
-      <x:c r="B33" s="9" t="str">
-        <x:v>ST-017</x:v>
-      </x:c>
-      <x:c r="C33" s="9" t="str">
-        <x:v>STA-04</x:v>
-      </x:c>
-      <x:c r="D33" s="9" t="n">
-        <x:v>45914</x:v>
-      </x:c>
-      <x:c r="E33" s="9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F33" s="9" t="str">
-        <x:v>Gerne wieder.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="9" t="str">
-        <x:v>FB-033</x:v>
-      </x:c>
-      <x:c r="B34" s="9" t="str">
-        <x:v>ST-005</x:v>
-      </x:c>
-      <x:c r="C34" s="9" t="str">
-        <x:v>STA-08</x:v>
-      </x:c>
-      <x:c r="D34" s="9" t="n">
-        <x:v>46068</x:v>
-      </x:c>
-      <x:c r="E34" s="9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F34" s="9" t="str">
-        <x:v>Ich habe mich wohlgefühlt.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="9" t="str">
-        <x:v>FB-034</x:v>
-      </x:c>
-      <x:c r="B35" s="9" t="str">
-        <x:v>ST-027</x:v>
-      </x:c>
-      <x:c r="C35" s="9" t="str">
-        <x:v>STA-06</x:v>
-      </x:c>
-      <x:c r="D35" s="9" t="n">
-        <x:v>45970</x:v>
-      </x:c>
-      <x:c r="E35" s="9" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F35" s="9" t="str">
-        <x:v>Organisation könnte klarer sein.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="9" t="str">
-        <x:v>FB-035</x:v>
-      </x:c>
-      <x:c r="B36" s="9" t="str">
-        <x:v>ST-002</x:v>
-      </x:c>
-      <x:c r="C36" s="9" t="str">
-        <x:v>STA-02</x:v>
-      </x:c>
-      <x:c r="D36" s="9" t="n">
-        <x:v>45844</x:v>
-      </x:c>
-      <x:c r="E36" s="9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F36" s="9" t="str">
-        <x:v>Schöne gemeinsame Aktivität.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="9" t="str">
-        <x:v>FB-036</x:v>
-      </x:c>
-      <x:c r="B37" s="9" t="str">
-        <x:v>ST-030</x:v>
-      </x:c>
-      <x:c r="C37" s="9" t="str">
-        <x:v>STA-04</x:v>
-      </x:c>
-      <x:c r="D37" s="9" t="n">
-        <x:v>45914</x:v>
-      </x:c>
-      <x:c r="E37" s="9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F37" s="9" t="str">
-        <x:v>Gerne wieder.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="9" t="str">
-        <x:v>FB-037</x:v>
-      </x:c>
-      <x:c r="B38" s="9" t="str">
-        <x:v>ST-017</x:v>
-      </x:c>
-      <x:c r="C38" s="9" t="str">
-        <x:v>STA-04</x:v>
-      </x:c>
-      <x:c r="D38" s="9" t="n">
-        <x:v>45914</x:v>
-      </x:c>
-      <x:c r="E38" s="9" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F38" s="9" t="str">
-        <x:v>War in Ordnung, aber etwas lang.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="9" t="str">
-        <x:v>FB-038</x:v>
-      </x:c>
-      <x:c r="B39" s="9" t="str">
-        <x:v>ST-030</x:v>
-      </x:c>
-      <x:c r="C39" s="9" t="str">
-        <x:v>STA-08</x:v>
-      </x:c>
-      <x:c r="D39" s="9" t="n">
-        <x:v>46068</x:v>
-      </x:c>
-      <x:c r="E39" s="9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F39" s="9" t="str">
-        <x:v>Schöne gemeinsame Aktivität.</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbfb9ff7c6ad94d86"/>
-  </x:tableParts>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.880000114440918" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="14.5" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.880000114440918" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="8" t="str">
+        <v>Feedback-ID</v>
+      </c>
+      <c r="B1" s="8" t="str">
+        <v>Teilnehmenden-ID</v>
+      </c>
+      <c r="C1" s="8" t="str">
+        <v>Aktivitäts-ID</v>
+      </c>
+      <c r="D1" s="12" t="str">
+        <v>Befragungsdatum</v>
+      </c>
+      <c r="E1" s="8" t="str">
+        <v>Zufriedenheit (1-5)</v>
+      </c>
+      <c r="F1" s="8" t="str">
+        <v>Kommentar</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="str">
+        <v>FB-001</v>
+      </c>
+      <c r="B2" s="9" t="str">
+        <v>ST-030</v>
+      </c>
+      <c r="C2" s="9" t="str">
+        <v>STA-07</v>
+      </c>
+      <c r="D2" s="9" t="n">
+        <v>46040</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="9" t="str">
+        <v>Schöne gemeinsame Aktivität.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="str">
+        <v>FB-002</v>
+      </c>
+      <c r="B3" s="9" t="str">
+        <v>ST-026</v>
+      </c>
+      <c r="C3" s="9" t="str">
+        <v>STA-06</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>45970</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="str">
+        <v>Schöne gemeinsame Aktivität.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="str">
+        <v>FB-003</v>
+      </c>
+      <c r="B4" s="9" t="str">
+        <v>ST-033</v>
+      </c>
+      <c r="C4" s="9" t="str">
+        <v>STA-01</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>45823</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="9" t="str">
+        <v>Gute Gelegenheit, andere kennenzulernen.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="str">
+        <v>FB-004</v>
+      </c>
+      <c r="B5" s="9" t="str">
+        <v>ST-022</v>
+      </c>
+      <c r="C5" s="9" t="str">
+        <v>STA-03</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>45886</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="9" t="str">
+        <v>Für mich nicht ganz passend.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="str">
+        <v>FB-005</v>
+      </c>
+      <c r="B6" s="9" t="str">
+        <v>ST-031</v>
+      </c>
+      <c r="C6" s="9" t="str">
+        <v>STA-05</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>45942</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="9" t="str">
+        <v>Für mich nicht ganz passend.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="str">
+        <v>FB-006</v>
+      </c>
+      <c r="B7" s="9" t="str">
+        <v>ST-021</v>
+      </c>
+      <c r="C7" s="9" t="str">
+        <v>STA-07</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>46040</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="9" t="str">
+        <v>Gerne wieder.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="str">
+        <v>FB-007</v>
+      </c>
+      <c r="B8" s="9" t="str">
+        <v>ST-034</v>
+      </c>
+      <c r="C8" s="9" t="str">
+        <v>STA-06</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>45970</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="9" t="str">
+        <v>Gerne wieder.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="str">
+        <v>FB-008</v>
+      </c>
+      <c r="B9" s="9" t="str">
+        <v>ST-002</v>
+      </c>
+      <c r="C9" s="9" t="str">
+        <v>STA-06</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>45970</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="9" t="str">
+        <v>Schöne gemeinsame Aktivität.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="str">
+        <v>FB-009</v>
+      </c>
+      <c r="B10" s="9" t="str">
+        <v>ST-017</v>
+      </c>
+      <c r="C10" s="9" t="str">
+        <v>STA-06</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>45970</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="9" t="str">
+        <v>Ich habe mich wohlgefühlt.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="str">
+        <v>FB-010</v>
+      </c>
+      <c r="B11" s="9" t="str">
+        <v>ST-014</v>
+      </c>
+      <c r="C11" s="9" t="str">
+        <v>STA-05</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>45942</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="9" t="str">
+        <v>Gerne wieder.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="str">
+        <v>FB-011</v>
+      </c>
+      <c r="B12" s="9" t="str">
+        <v>ST-030</v>
+      </c>
+      <c r="C12" s="9" t="str">
+        <v>STA-06</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>45970</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="9" t="str">
+        <v>Organisation könnte klarer sein.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="str">
+        <v>FB-012</v>
+      </c>
+      <c r="B13" s="9" t="str">
+        <v>ST-008</v>
+      </c>
+      <c r="C13" s="9" t="str">
+        <v>STA-06</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>45970</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="9" t="str">
+        <v>Gerne wieder.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="str">
+        <v>FB-013</v>
+      </c>
+      <c r="B14" s="9" t="str">
+        <v>ST-009</v>
+      </c>
+      <c r="C14" s="9" t="str">
+        <v>STA-02</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>45844</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="9" t="str">
+        <v>Ich habe mich wohlgefühlt.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="str">
+        <v>FB-014</v>
+      </c>
+      <c r="B15" s="9" t="str">
+        <v>ST-008</v>
+      </c>
+      <c r="C15" s="9" t="str">
+        <v>STA-01</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>45823</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="9" t="str">
+        <v>Gute Gelegenheit, andere kennenzulernen.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="str">
+        <v>FB-015</v>
+      </c>
+      <c r="B16" s="9" t="str">
+        <v>ST-027</v>
+      </c>
+      <c r="C16" s="9" t="str">
+        <v>STA-06</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>45970</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="9" t="str">
+        <v>Gute Gelegenheit, andere kennenzulernen.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="str">
+        <v>FB-016</v>
+      </c>
+      <c r="B17" s="9" t="str">
+        <v>ST-029</v>
+      </c>
+      <c r="C17" s="9" t="str">
+        <v>STA-05</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>45942</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="9" t="str">
+        <v>Gerne wieder.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="str">
+        <v>FB-017</v>
+      </c>
+      <c r="B18" s="9" t="str">
+        <v>ST-030</v>
+      </c>
+      <c r="C18" s="9" t="str">
+        <v>STA-05</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>45942</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" s="9" t="str">
+        <v>Gerne wieder.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="str">
+        <v>FB-018</v>
+      </c>
+      <c r="B19" s="9" t="str">
+        <v>ST-026</v>
+      </c>
+      <c r="C19" s="9" t="str">
+        <v>STA-03</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>45886</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="9" t="str">
+        <v>Ich habe mich wohlgefühlt.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="str">
+        <v>FB-019</v>
+      </c>
+      <c r="B20" s="9" t="str">
+        <v>ST-029</v>
+      </c>
+      <c r="C20" s="9" t="str">
+        <v>STA-03</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>45886</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="9" t="str">
+        <v>Organisation könnte klarer sein.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="str">
+        <v>FB-020</v>
+      </c>
+      <c r="B21" s="9" t="str">
+        <v>ST-028</v>
+      </c>
+      <c r="C21" s="9" t="str">
+        <v>STA-08</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>46068</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" s="9" t="str">
+        <v>Schöne gemeinsame Aktivität.</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="str">
+        <v>FB-021</v>
+      </c>
+      <c r="B22" s="9" t="str">
+        <v>ST-018</v>
+      </c>
+      <c r="C22" s="9" t="str">
+        <v>STA-03</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>45886</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="9" t="str">
+        <v>Ich habe mich wohlgefühlt.</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="str">
+        <v>FB-022</v>
+      </c>
+      <c r="B23" s="9" t="str">
+        <v>ST-021</v>
+      </c>
+      <c r="C23" s="9" t="str">
+        <v>STA-02</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>45844</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="9" t="str">
+        <v>Schöne gemeinsame Aktivität.</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="str">
+        <v>FB-023</v>
+      </c>
+      <c r="B24" s="9" t="str">
+        <v>ST-013</v>
+      </c>
+      <c r="C24" s="9" t="str">
+        <v>STA-02</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>45844</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="9" t="str">
+        <v>Gute Gelegenheit, andere kennenzulernen.</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="str">
+        <v>FB-024</v>
+      </c>
+      <c r="B25" s="9" t="str">
+        <v>ST-031</v>
+      </c>
+      <c r="C25" s="9" t="str">
+        <v>STA-03</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>45886</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="9" t="str">
+        <v>Schöne gemeinsame Aktivität.</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="str">
+        <v>FB-025</v>
+      </c>
+      <c r="B26" s="9" t="str">
+        <v>ST-031</v>
+      </c>
+      <c r="C26" s="9" t="str">
+        <v>STA-07</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>46040</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="9" t="str">
+        <v>Gute Gelegenheit, andere kennenzulernen.</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="str">
+        <v>FB-026</v>
+      </c>
+      <c r="B27" s="9" t="str">
+        <v>ST-023</v>
+      </c>
+      <c r="C27" s="9" t="str">
+        <v>STA-02</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>45844</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" s="9" t="str">
+        <v>Ich habe mich wohlgefühlt.</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="str">
+        <v>FB-027</v>
+      </c>
+      <c r="B28" s="9" t="str">
+        <v>ST-015</v>
+      </c>
+      <c r="C28" s="9" t="str">
+        <v>STA-06</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>45970</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" s="9" t="str">
+        <v>Gute Gelegenheit, andere kennenzulernen.</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="str">
+        <v>FB-028</v>
+      </c>
+      <c r="B29" s="9" t="str">
+        <v>ST-033</v>
+      </c>
+      <c r="C29" s="9" t="str">
+        <v>STA-07</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>46040</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="9" t="str">
+        <v>Für mich nicht ganz passend.</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="str">
+        <v>FB-029</v>
+      </c>
+      <c r="B30" s="9" t="str">
+        <v>ST-005</v>
+      </c>
+      <c r="C30" s="9" t="str">
+        <v>STA-03</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>45886</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" s="9" t="str">
+        <v>Schöne gemeinsame Aktivität.</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="str">
+        <v>FB-030</v>
+      </c>
+      <c r="B31" s="9" t="str">
+        <v>ST-001</v>
+      </c>
+      <c r="C31" s="9" t="str">
+        <v>STA-06</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>45970</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="9" t="str">
+        <v>War in Ordnung, aber etwas lang.</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="str">
+        <v>FB-031</v>
+      </c>
+      <c r="B32" s="9" t="str">
+        <v>ST-005</v>
+      </c>
+      <c r="C32" s="9" t="str">
+        <v>STA-05</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>45942</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" s="9" t="str">
+        <v>Schöne gemeinsame Aktivität.</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="str">
+        <v>FB-032</v>
+      </c>
+      <c r="B33" s="9" t="str">
+        <v>ST-017</v>
+      </c>
+      <c r="C33" s="9" t="str">
+        <v>STA-04</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>45914</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="9" t="str">
+        <v>Gerne wieder.</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="str">
+        <v>FB-033</v>
+      </c>
+      <c r="B34" s="9" t="str">
+        <v>ST-005</v>
+      </c>
+      <c r="C34" s="9" t="str">
+        <v>STA-08</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>46068</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" s="9" t="str">
+        <v>Ich habe mich wohlgefühlt.</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="str">
+        <v>FB-034</v>
+      </c>
+      <c r="B35" s="9" t="str">
+        <v>ST-027</v>
+      </c>
+      <c r="C35" s="9" t="str">
+        <v>STA-06</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>45970</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" s="9" t="str">
+        <v>Organisation könnte klarer sein.</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="str">
+        <v>FB-035</v>
+      </c>
+      <c r="B36" s="9" t="str">
+        <v>ST-002</v>
+      </c>
+      <c r="C36" s="9" t="str">
+        <v>STA-02</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>45844</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" s="9" t="str">
+        <v>Schöne gemeinsame Aktivität.</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="str">
+        <v>FB-036</v>
+      </c>
+      <c r="B37" s="9" t="str">
+        <v>ST-030</v>
+      </c>
+      <c r="C37" s="9" t="str">
+        <v>STA-04</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>45914</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="9" t="str">
+        <v>Gerne wieder.</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="str">
+        <v>FB-037</v>
+      </c>
+      <c r="B38" s="9" t="str">
+        <v>ST-017</v>
+      </c>
+      <c r="C38" s="9" t="str">
+        <v>STA-04</v>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>45914</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" s="9" t="str">
+        <v>War in Ordnung, aber etwas lang.</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="str">
+        <v>FB-038</v>
+      </c>
+      <c r="B39" s="9" t="str">
+        <v>ST-030</v>
+      </c>
+      <c r="C39" s="9" t="str">
+        <v>STA-08</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>46068</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" s="9" t="str">
+        <v>Schöne gemeinsame Aktivität.</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>FB-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ST-014</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>STA-05</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>45942</v>
+      </c>
+      <c r="E40">
+        <v>5</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ich habe mich in der Gruppe sofort wohlfuehlt und spaeter noch Telefonnummern mit zwei anderen Teilnehmenden ausgetauscht.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>FB-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ST-011</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>STA-07</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>46041</v>
+      </c>
+      <c r="E41">
+        <v>4</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Der Ausflug hat gutgetan, weil ich sonst selten aus dem Stadtteil herauskomme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>FB-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ST-028</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>STA-08</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>46069</v>
+      </c>
+      <c r="E42">
+        <v>5</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Besonders schoen war, dass genug Zeit fuer Gespraeche blieb und niemand gedraengt wurde.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="Rbfb9ff7c6ad94d86"/>
+  </tableParts>
+</worksheet>
 </file>